--- a/data/trans_orig/IP29_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37962</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50616</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>70858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>56414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71380</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>69232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83101</t>
+          <t>84392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128816</t>
+          <t>130014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150256</t>
+          <t>150550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61340</t>
+          <t>61371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84768</t>
+          <t>84648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91121</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133336</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167312</t>
+          <t>165582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>162698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186006</t>
+          <t>185975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159120</t>
+          <t>159639</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183073</t>
+          <t>184026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330275</t>
+          <t>332005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364251</t>
+          <t>363055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49194</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78478</t>
+          <t>79533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91099</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>101322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115636</t>
+          <t>115779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180819</t>
+          <t>179764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203053</t>
+          <t>202360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52073</t>
+          <t>51664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>71839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>53978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74650</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111251</t>
+          <t>110494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>141397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116311</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136368</t>
+          <t>136777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127355</t>
+          <t>127061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148132</t>
+          <t>148027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249312</t>
+          <t>249049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279195</t>
+          <t>279952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187669</t>
+          <t>186301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226564</t>
+          <t>225741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180081</t>
+          <t>180744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218392</t>
+          <t>218650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379329</t>
+          <t>379490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433388</t>
+          <t>432192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426201</t>
+          <t>427024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465096</t>
+          <t>466464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477045</t>
+          <t>476787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515356</t>
+          <t>514693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914814</t>
+          <t>916010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968873</t>
+          <t>968712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>30681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48344</t>
+          <t>48076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56262</t>
+          <t>57096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80451</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87808</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105826</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97235</t>
+          <t>97531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114109</t>
+          <t>114372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191757</t>
+          <t>191028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215946</t>
+          <t>215112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>48593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70368</t>
+          <t>69333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54817</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>77819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109926</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141888</t>
+          <t>142989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164625</t>
+          <t>165660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185999</t>
+          <t>186400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186160</t>
+          <t>187093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210095</t>
+          <t>210687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358017</t>
+          <t>356916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389979</t>
+          <t>390285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72357</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>98894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98168</t>
+          <t>97950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117488</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112532</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129583</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>215014</t>
+          <t>213984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240521</t>
+          <t>240752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73262</t>
+          <t>73888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100115</t>
+          <t>99881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115917</t>
+          <t>116507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>134564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121778</t>
+          <t>120929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140877</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243484</t>
+          <t>243718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270337</t>
+          <t>269711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207315</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>155443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194490</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>337279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392290</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487886</t>
+          <t>488110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525055</t>
+          <t>527491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>538899</t>
+          <t>539804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>577652</t>
+          <t>577946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1036301</t>
+          <t>1039680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093714</t>
+          <t>1091312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36445</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>37911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62959</t>
+          <t>62958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85767</t>
+          <t>86314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>69364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86150</t>
+          <t>86562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>82490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98314</t>
+          <t>97969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157230</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180038</t>
+          <t>180039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72909</t>
+          <t>74236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69646</t>
+          <t>70348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94142</t>
+          <t>94630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127894</t>
+          <t>130213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161616</t>
+          <t>165237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135769</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155899</t>
+          <t>154930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161894</t>
+          <t>161406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>186390</t>
+          <t>185688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303098</t>
+          <t>299477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336820</t>
+          <t>334501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57191</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55903</t>
+          <t>56532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77477</t>
+          <t>77139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>128078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131708</t>
+          <t>133062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151111</t>
+          <t>151643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106879</t>
+          <t>107217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128453</t>
+          <t>127824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244519</t>
+          <t>245177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274605</t>
+          <t>275520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>56903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52511</t>
+          <t>53991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76400</t>
+          <t>77963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103557</t>
+          <t>105771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129187</t>
+          <t>128727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113841</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132675</t>
+          <t>132243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228962</t>
+          <t>226748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256119</t>
+          <t>254556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181116</t>
+          <t>181939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217984</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>198247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>240145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,47 +6048,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>390945</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>448340</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>27,66%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>420535</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>391273</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>448977</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468355</t>
+          <t>467556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>505223</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486306</t>
+          <t>487000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525983</t>
+          <t>528898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,47 +6161,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>992949</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>965144</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1022539</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>72,34%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>992949</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>964507</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1022211</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>68,24%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>29799</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22387</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36981</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>30238</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23314</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38001</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23244</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37926</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29799</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22065</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37225</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70858</t>
+          <t>70522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76658</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69476</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84070</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64177</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56414</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71101</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56489</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71171</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,97%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>75,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76658</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69232</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84392</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>72,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130014</t>
+          <t>130350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150550</t>
+          <t>151480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>106457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>106457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>106457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>94415</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>94415</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>94415</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>106457</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>106457</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>106457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77988</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66788</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>89906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>73035</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>61371</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84648</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>62808</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>84044</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77988</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>66215</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>90602</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134532</t>
+          <t>135467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165582</t>
+          <t>167771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>172253</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>160335</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>183453</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>174311</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>162698</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185975</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>163302</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184538</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>172253</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>159639</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>184026</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332005</t>
+          <t>329816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>363055</t>
+          <t>362120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>247346</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>247346</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>247346</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27396</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20403</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35900</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>40046</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31796</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48757</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32199</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49067</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27396</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20955</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35412</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56937</t>
+          <t>55563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79533</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109338</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100834</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>116331</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82517</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73806</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90767</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>73496</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90364</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>109338</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>101322</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>115779</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179764</t>
+          <t>178787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202360</t>
+          <t>203734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136734</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>122563</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>122563</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>122563</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63652</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52839</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>74066</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61781</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51664</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>71839</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52030</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71930</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>63652</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>53978</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>74944</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110494</t>
+          <t>110007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141397</t>
+          <t>140758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>138353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>127939</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>149166</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>126660</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>116602</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>136777</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>116511</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>136411</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>138353</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>127061</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>148027</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249049</t>
+          <t>249688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279952</t>
+          <t>280439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202005</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202005</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188441</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202005</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202005</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>218963</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>186301</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>225741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>186056</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>223047</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>198834</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>180744</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>218650</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379490</t>
+          <t>377129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432192</t>
+          <t>432518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>496603</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476474</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>515836</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>447665</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>427024</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>466464</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>429718</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>466709</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>496603</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>476787</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>514693</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>916010</t>
+          <t>915684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968712</t>
+          <t>971073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>695437</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>977</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>652765</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>695437</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29179</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21366</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38212</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38909</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30681</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48076</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30443</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48003</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29179</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21684</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38525</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57096</t>
+          <t>56615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81180</t>
+          <t>81260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106877</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>97844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>114690</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97243</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88076</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105471</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88149</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105709</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>71,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>106877</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>97531</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114372</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191028</t>
+          <t>190948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215112</t>
+          <t>215593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>136056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>136056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>136056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136152</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136152</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136152</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>136056</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>136056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>136056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65932</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55362</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>78917</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58948</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48593</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>69333</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>47972</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69877</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>65932</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>54225</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>77819</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109620</t>
+          <t>110410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142989</t>
+          <t>141708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198980</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185995</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209550</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>176045</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>165660</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>186400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>165116</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>187021</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>198980</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>187093</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210687</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356916</t>
+          <t>358197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>390285</t>
+          <t>389495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234993</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234993</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34675</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27104</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43956</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48986</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39486</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59093</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40417</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58544</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34675</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>26423</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43800</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98894</t>
+          <t>96585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>121160</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111879</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128731</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>108057</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97950</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117557</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98499</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>116626</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>68,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>121160</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>112035</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>129412</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213984</t>
+          <t>216293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240752</t>
+          <t>242325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44697</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35054</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54681</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>41068</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32449</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50506</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32812</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50280</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44697</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36552</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55657</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73888</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99881</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131889</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121905</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>125945</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>116507</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134564</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>116733</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134201</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>131889</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>120929</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>140034</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243718</t>
+          <t>242951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269711</t>
+          <t>270502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167013</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>156425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>193734</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>167710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>207091</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>167451</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>205543</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>174484</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>155443</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>193585</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337279</t>
+          <t>333567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388911</t>
+          <t>390742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>558905</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>539655</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>576964</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>76,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>507290</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>488110</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>527491</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489658</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>527750</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>72,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>558905</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>539804</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>577946</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>76,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1039680</t>
+          <t>1037849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091312</t>
+          <t>1095024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>733389</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>695201</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>733389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29312</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22273</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37036</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,76%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>44472</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36033</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53231</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34862</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52686</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29312</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22432</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37911</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62958</t>
+          <t>63376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86314</t>
+          <t>85271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>91089</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83365</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98128</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78123</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86562</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69909</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87733</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>91089</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82490</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97969</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156683</t>
+          <t>157726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180039</t>
+          <t>179621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>120401</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>120401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>122595</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>122595</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>122595</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>120401</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>120401</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>120401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81397</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70300</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93940</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>63171</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53748</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74236</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52226</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>74536</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>81397</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>70348</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>94630</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130213</t>
+          <t>127372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165237</t>
+          <t>160417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>174639</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>162096</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>185736</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>145507</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134442</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>134142</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>156452</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>174639</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>161406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>185688</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>299477</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>334501</t>
+          <t>337342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>256036</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208678</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>256036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66746</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56299</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76705</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46059</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37256</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55837</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37421</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57131</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>24,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66746</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>56532</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>77139</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128078</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117610</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>107651</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>142840</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133062</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>151643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131768</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>151478</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>75,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>117610</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>107217</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>127824</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245177</t>
+          <t>245093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>275520</t>
+          <t>273867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34174</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>46079</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37440</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>56903</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36705</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56208</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43300</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34109</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53991</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77963</t>
+          <t>76472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105771</t>
+          <t>104129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123052</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>113213</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132178</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>120088</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>109264</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128727</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>109959</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>129462</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123052</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>112361</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>132243</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>73,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226748</t>
+          <t>228390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254556</t>
+          <t>256047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166352</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166167</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166167</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166167</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>166352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>200495</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>243531</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>199781</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>181939</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>218783</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181532</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>220370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>198247</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>240145</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390945</t>
+          <t>393370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>449071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>506391</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>483614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>526650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>486558</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>467556</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>504400</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>465969</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>504807</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>506391</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>487000</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>528898</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>965144</t>
+          <t>964413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1022539</t>
+          <t>1020114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>727145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>686339</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>727145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
